--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,414 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128495668</v>
+      </c>
+      <c r="B3" t="n">
+        <v>88709</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tvärån, Tvärån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>407985</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7023809</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Lämnad grannaturskogsrest i mitten av ett hygge</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128495700</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92149</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tvärån, Tvärån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>407831</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7023800</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lämnad grannaturskogsrest i mitten av ett hygge</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128495642</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tvärån, Tvärån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>407998</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7023811</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lämnad grannaturskogsrest i mitten av ett hygge</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128495756</v>
+      </c>
+      <c r="B6" t="n">
+        <v>75171</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tvärån, Tvärån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>407820</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7023813</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lämnad grannaturskogsrest i mitten av ett hygge</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>128495668</v>
       </c>
       <c r="B3" t="n">
-        <v>88709</v>
+        <v>88715</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128495700</v>
       </c>
       <c r="B4" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128495642</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128495756</v>
       </c>
       <c r="B6" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>128495668</v>
       </c>
       <c r="B3" t="n">
-        <v>88715</v>
+        <v>88721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128495700</v>
       </c>
       <c r="B4" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>128495668</v>
       </c>
       <c r="B3" t="n">
-        <v>88721</v>
+        <v>88723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128495700</v>
       </c>
       <c r="B4" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128495642</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128495756</v>
       </c>
       <c r="B6" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128495700</v>
       </c>
       <c r="B4" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>128495668</v>
       </c>
       <c r="B3" t="n">
-        <v>88723</v>
+        <v>88750</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128495700</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128495642</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128495756</v>
       </c>
       <c r="B6" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>128495668</v>
       </c>
       <c r="B3" t="n">
-        <v>88750</v>
+        <v>88754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128495700</v>
       </c>
       <c r="B4" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128495642</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128495756</v>
       </c>
       <c r="B6" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>128495668</v>
       </c>
       <c r="B3" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128495700</v>
       </c>
       <c r="B4" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>128495668</v>
       </c>
       <c r="B3" t="n">
-        <v>88755</v>
+        <v>88759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128495700</v>
       </c>
       <c r="B4" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128495642</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128495756</v>
       </c>
       <c r="B6" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>128495668</v>
       </c>
       <c r="B3" t="n">
-        <v>88759</v>
+        <v>88764</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128495700</v>
       </c>
       <c r="B4" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128495642</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128495756</v>
       </c>
       <c r="B6" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>128495668</v>
       </c>
       <c r="B3" t="n">
-        <v>88766</v>
+        <v>88771</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128495700</v>
       </c>
       <c r="B4" t="n">
-        <v>92213</v>
+        <v>92218</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128495642</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>128495756</v>
       </c>
       <c r="B6" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67560920</v>
+        <v>67560934</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407814.8477526308</v>
+        <v>407959</v>
       </c>
       <c r="R2" t="n">
-        <v>7023835.054443367</v>
+        <v>7023859</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,9 @@
           <t>2017-09-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128495668</v>
+        <v>128495700</v>
       </c>
       <c r="B3" t="n">
-        <v>88771</v>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4405</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407985</v>
+        <v>407831</v>
       </c>
       <c r="R3" t="n">
-        <v>7023809</v>
+        <v>7023800</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128495700</v>
+        <v>128495668</v>
       </c>
       <c r="B4" t="n">
-        <v>92218</v>
+        <v>89143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>4405</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407831</v>
+        <v>407985</v>
       </c>
       <c r="R4" t="n">
-        <v>7023800</v>
+        <v>7023809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,14 +976,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128495642</v>
+        <v>67560925</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1027,17 +1007,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tvärån, Tvärån, Jmt</t>
+          <t>Tvärsätt V, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407998</v>
+        <v>407783</v>
       </c>
       <c r="R5" t="n">
-        <v>7023811</v>
+        <v>7023789</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,12 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2017-09-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2017-09-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,53 +1057,48 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Lämnad grannaturskogsrest i mitten av ett hygge</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128495756</v>
+        <v>128495642</v>
       </c>
       <c r="B6" t="n">
-        <v>83010</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407820</v>
+        <v>407998</v>
       </c>
       <c r="R6" t="n">
-        <v>7023813</v>
+        <v>7023811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,6 +1172,914 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128495756</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tvärån, Tvärån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>407820</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7023813</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lämnad grannaturskogsrest i mitten av ett hygge</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>67560941</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tvärsätt V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>407976</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7023838</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>67560917</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tvärsätt V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>407912</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7023753</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>67560920</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tvärsätt V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>407815</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7023835</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>67560921</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tvärsätt V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>407925</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7023791</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>67560922</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tvärsätt V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>407908</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7023804</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>67560924</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tvärsätt V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>407971</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7023851</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>67560942</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tvärsätt V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>408001</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7023830</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska hackmärken</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>67560940</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tvärsätt V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>407984</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7023855</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4775-2025 artfynd.xlsx
+++ b/artfynd/A 4775-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560934</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495700</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495668</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560925</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495642</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495756</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560941</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560917</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560920</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560921</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560922</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560924</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1983,6 +2048,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560942</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2080,8 +2150,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67560940</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>